--- a/dcf/XEL.xlsx
+++ b/dcf/XEL.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.03539136293174203</v>
+        <v>0.03533348918341619</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.04039136293174202</v>
+        <v>0.04033348918341619</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.04539136293174203</v>
+        <v>0.0453334891834162</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.05039136293174203</v>
+        <v>0.05033348918341619</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.05539136293174202</v>
+        <v>0.05533348918341619</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.06039136293174203</v>
+        <v>0.0603334891834162</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.06539136293174203</v>
+        <v>0.06533348918341619</v>
       </c>
     </row>
     <row r="5">
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>173.141260188154</v>
+        <v>173.2414912562497</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>164.6918634124721</v>
+        <v>164.7873308214312</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>156.6427082048095</v>
+        <v>156.7336683089673</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>148.9723150255031</v>
+        <v>149.0590090527142</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>141.6604685406628</v>
+        <v>141.7431235569618</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>134.6881371962625</v>
+        <v>134.766967004617</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>128.0373982745138</v>
+        <v>128.112604252454</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>188.2599859597601</v>
+        <v>188.3686703181967</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>179.0995146422238</v>
+        <v>179.2029990337793</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>170.3759002102518</v>
+        <v>170.4744654408854</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>162.0656159079925</v>
+        <v>162.1595261795949</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>154.1465226097344</v>
+        <v>154.2360265804999</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>146.5977804176067</v>
+        <v>146.6831121898848</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>139.3997662913152</v>
+        <v>139.4811463322125</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>203.3787117313662</v>
+        <v>203.4958493801437</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>193.5071658719756</v>
+        <v>193.6186672461274</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>184.1090922156941</v>
+        <v>184.2152625728035</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>175.1589167904818</v>
+        <v>175.2600433064758</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>166.632576678806</v>
+        <v>166.728929604038</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>158.5074236389509</v>
+        <v>158.5992573751524</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>150.7621343081167</v>
+        <v>150.849688411971</v>
       </c>
     </row>
     <row r="8">
@@ -1213,25 +1213,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>218.4974375029723</v>
+        <v>218.6230284420907</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>207.9148171017273</v>
+        <v>208.0343354584755</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>197.8422842211365</v>
+        <v>197.9560597047216</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>188.2522176729711</v>
+        <v>188.3605604333565</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>179.1186307478775</v>
+        <v>179.2218326275761</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>170.4170668602951</v>
+        <v>170.5154025604202</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>162.1245023249182</v>
+        <v>162.2182304917296</v>
       </c>
     </row>
     <row r="9">
@@ -1239,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>233.6161632745784</v>
+        <v>233.7502075040377</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>222.3224683314791</v>
+        <v>222.4500036708236</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>211.5754762265788</v>
+        <v>211.6968568366396</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>201.3455185554604</v>
+        <v>201.4610775602372</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>191.6046848169491</v>
+        <v>191.7147356511142</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>182.3267100816392</v>
+        <v>182.4315477456879</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>173.4868703417196</v>
+        <v>173.5867725714882</v>
       </c>
     </row>
     <row r="10">
@@ -1265,25 +1265,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>248.7348890461846</v>
+        <v>248.8773865659847</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>236.7301195612308</v>
+        <v>236.8656718831717</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>225.3086682320211</v>
+        <v>225.4376539685576</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>214.4388194379498</v>
+        <v>214.561594687118</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>204.0907388860207</v>
+        <v>204.2076386746523</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>194.2363533029833</v>
+        <v>194.3476929309556</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>184.8492383585211</v>
+        <v>184.9553146512467</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>263.8536148177907</v>
+        <v>264.0045656279316</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>251.1377707909825</v>
+        <v>251.2813400955198</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>239.0418602374634</v>
+        <v>239.1784511004757</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>227.5321203204391</v>
+        <v>227.6621118139987</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>216.5767929550923</v>
+        <v>216.7005416981904</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>206.1459965243275</v>
+        <v>206.2638381162233</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>196.2116063753226</v>
+        <v>196.3238567310052</v>
       </c>
     </row>
     <row r="13">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>81.95999908447266</v>
+        <v>81.26000213623047</v>
       </c>
     </row>
     <row r="14">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.05039136293174203</v>
+        <v>0.05033348918341619</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.144417702441459</v>
+        <v>1.144349682673351</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>81.95999908447266</v>
+        <v>81.26000213623047</v>
       </c>
     </row>
     <row r="49">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>188.2522176729711</v>
+        <v>188.3605604333565</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>280.8400494798339</v>
+        <v>280.9959146183331</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>119.7031965587764</v>
+        <v>119.7768662789057</v>
       </c>
     </row>
     <row r="59">
